--- a/Data/EXCEL/Transfer/salemon/202602/9928-salemon-202602.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202602/9928-salemon-202602.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1600B2D1-51E2-4D33-B1D5-B9550EECB884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A85CA143-C582-4FFA-B514-9766304C2BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{830A26D7-4CD0-4544-92AC-056B80AFF5D3}"/>
+    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{757AE322-05CE-41B2-B07E-129B796CD501}"/>
   </bookViews>
   <sheets>
     <sheet name="9928-salemon-202602" sheetId="2" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272FE534-5329-4F29-805B-1A8A3158AEFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838D69F0-7E15-4ECD-B4B6-D8F92CD1EC39}">
   <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
